--- a/datasets/subsidy_validation_datasets2.xlsx
+++ b/datasets/subsidy_validation_datasets2.xlsx
@@ -22,7 +22,7 @@
     <t>Farm Size (ha)</t>
   </si>
   <si>
-    <t>Crop Yield Before (tons)</t>
+    <t>Average Yield Before (tons)</t>
   </si>
   <si>
     <t>Crop Yield After (tons)</t>
@@ -104,7 +104,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -496,7 +496,7 @@
     <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -525,7 +525,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
@@ -552,7 +552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
@@ -581,7 +581,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -610,7 +610,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
@@ -639,7 +639,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -664,7 +664,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -693,7 +693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
@@ -722,7 +722,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
@@ -751,7 +751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
@@ -780,7 +780,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
@@ -809,7 +809,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="4" t="s">
         <v>9</v>
       </c>
@@ -838,7 +838,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="4" t="s">
         <v>9</v>
       </c>
@@ -867,7 +867,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="4" t="s">
         <v>9</v>
       </c>
@@ -894,7 +894,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
@@ -919,7 +919,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="4" t="s">
         <v>9</v>
       </c>
@@ -948,7 +948,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="4" t="s">
         <v>9</v>
       </c>
@@ -977,7 +977,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="4" t="s">
         <v>9</v>
       </c>
